--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fileVersion appName="HCell" lastEdited="12.0" lowestEdited="12.0" rupBuild="0.535"/>
+  <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\UnityBasic_6\JsonConverter\ExcelFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294934950" windowHeight="6150"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="19260" windowHeight="7368"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,51 +14,93 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="39">
+  <x:si>
+    <x:t>딸기, 겨울에 더 맛있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Starwberry_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>딸기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>의문의 모자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화폐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
   <x:si>
     <x:t>Item_Equip_Hat_1</x:t>
   </x:si>
   <x:si>
+    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Icon_Item_Corn</x:t>
   </x:si>
   <x:si>
-    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>의문의 모자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역에 나타나는 금화</x:t>
   </x:si>
   <x:si>
     <x:t>Equipment</x:t>
   </x:si>
   <x:si>
-    <x:t>지역에 나타나는 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
+    <x:t>Item_Potato_1</x:t>
   </x:si>
   <x:si>
     <x:t>SellingPrice</x:t>
@@ -72,22 +109,16 @@
     <x:t>Item_DummyBox_1</x:t>
   </x:si>
   <x:si>
+    <x:t>착용하면 공격력이 강해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
     <x:t>MaxStackCount</x:t>
   </x:si>
   <x:si>
-    <x:t>착용하면 공격력이 강해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
+    <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
   </x:si>
   <x:si>
     <x:t>Description</x:t>
@@ -96,44 +127,17 @@
     <x:t>IconPath</x:t>
   </x:si>
   <x:si>
-    <x:t>상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
+    <x:t>Icon/Icon_Item_Gold_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Box_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="9">
     <x:font>
       <x:name val="Arial"/>
       <x:sz val="10"/>
@@ -165,6 +169,11 @@
       <x:color rgb="ff000000"/>
     </x:font>
     <x:font>
+      <x:name val="돋움"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
       <x:name val="&quot;맑은 고딕&quot;"/>
       <x:sz val="10"/>
       <x:color rgb="ff000000"/>
@@ -185,7 +194,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffffffff"/>
-        <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -215,7 +223,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffd2f2db"/>
-        <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -226,7 +233,7 @@
     </x:fill>
   </x:fills>
   <x:borders count="2">
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left>
         <x:color rgb="ff000000"/>
       </x:left>
@@ -234,29 +241,77 @@
         <x:color rgb="ff000000"/>
       </x:right>
       <x:top>
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:top>
       <x:bottom>
         <x:color rgb="ff000000"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left style="thin">
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:left>
       <x:right style="thin">
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:right>
       <x:top style="thin">
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="1">
+  <x:cellStyleXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -264,22 +319,22 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -294,7 +349,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -306,19 +361,20 @@
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
-    <x:cellStyle name="표준" xfId="0" builtinId="0"/>
+    <x:cellStyle xfId="0" builtinId="0"/>
   </x:cellStyles>
-  <x:dxfs count="12">
+  <x:dxfs count="30">
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -401,6 +457,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -435,6 +492,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -479,6 +537,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -522,6 +581,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -529,10 +589,10 @@
           </x:font>
           <x:border>
             <x:left>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:left>
             <x:right>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:right>
             <x:top style="medium">
               <x:color rgb="ff6182d6"/>
@@ -541,10 +601,10 @@
               <x:color rgb="ff6182d6"/>
             </x:bottom>
             <x:vertical>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:vertical>
             <x:horizontal>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:horizontal>
           </x:border>
         </x:dxf>
@@ -556,10 +616,10 @@
           </x:font>
           <x:border>
             <x:left>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:left>
             <x:right>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:right>
             <x:top style="medium">
               <x:color rgb="ff6182d6"/>
@@ -568,10 +628,10 @@
               <x:color rgb="ff6182d6"/>
             </x:bottom>
             <x:vertical>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:vertical>
             <x:horizontal>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:horizontal>
           </x:border>
         </x:dxf>
@@ -606,6 +666,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -626,6 +687,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -656,6 +718,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -681,6 +744,457 @@
         </x:dxf>
       </mc:Fallback>
     </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9d9d9"/>
+          <x:bgColor rgb="ffd9d9d9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9d9d9"/>
+          <x:bgColor rgb="ffd9d9d9"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:left style="thin">
+          <x:color rgb="ffbfbfbf"/>
+        </x:left>
+        <x:right style="thin">
+          <x:color rgb="ffbfbfbf"/>
+        </x:right>
+      </x:border>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9d9d9"/>
+          <x:bgColor rgb="ffd9d9d9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:bottom style="thin">
+          <x:color rgb="ff8db6f9"/>
+        </x:bottom>
+      </x:border>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:bottom style="thin">
+          <x:color rgb="ff8db6f9"/>
+        </x:bottom>
+      </x:border>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+            <x:horizontal style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+          </x:font>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+            <x:horizontal style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff4285f4"/>
+              <x:bgColor rgb="ff4285f4"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff4285f4"/>
+              <x:bgColor rgb="ff4285f4"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:top style="double">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:top style="double">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
   </x:dxfs>
   <x:tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <x:tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
@@ -709,7 +1223,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Sheets">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -904,9 +1418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr codeName="Sheet1">
-    <x:outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
-  </x:sheetPr>
+  <x:sheetPr codeName="Sheet1"/>
   <x:dimension ref="A1:M35"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
@@ -921,80 +1433,80 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:8" ht="13.19999999999999928946">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:8" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>23</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D3" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>24</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>20</x:v>
@@ -1003,7 +1515,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -1013,19 +1525,19 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>1000</x:v>
@@ -1034,7 +1546,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1044,19 +1556,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>0</x:v>
@@ -1065,7 +1577,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -1074,19 +1586,19 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D7" s="4" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="4" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>100</x:v>
@@ -1095,7 +1607,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1105,19 +1617,19 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>20</x:v>
@@ -1126,7 +1638,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
@@ -1135,9 +1647,15 @@
       <x:c r="M8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A9" s="6"/>
-      <x:c r="B9" s="6"/>
-      <x:c r="C9" s="6"/>
+      <x:c r="A9" s="6" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="s">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="D9" s="4"/>
       <x:c r="E9" s="4"/>
       <x:c r="F9" s="4"/>
@@ -2305,7 +2823,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -14,123 +14,126 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="39">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
+  <x:si>
+    <x:t>Icon/Icon_Item_Box_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>착용하면 공격력이 강해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
   <x:si>
     <x:t>딸기, 겨울에 더 맛있다.</x:t>
   </x:si>
   <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_DummyBox_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화폐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>딸기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Corn</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_Starwberry_1</x:t>
   </x:si>
   <x:si>
-    <x:t>딸기</x:t>
+    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
   </x:si>
   <x:si>
     <x:t>의문의 모자</x:t>
   </x:si>
   <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
     <x:t>Legend</x:t>
   </x:si>
   <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Corn</x:t>
+    <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
     <x:t>ItemType</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역에 나타나는 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Gold_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지역에 나타나는 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_DummyBox_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>착용하면 공격력이 강해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
+    <x:t>Description</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Box_1</x:t>
+    <x:t>Icon/Icon_Item_Strawberry_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1426,87 +1429,88 @@
     <x:col min="2" max="2" width="19.5703125" style="2" customWidth="1"/>
     <x:col min="3" max="3" width="50.7109375" style="2" customWidth="1"/>
     <x:col min="4" max="4" width="26.5703125" style="2" customWidth="1"/>
-    <x:col min="5" max="7" width="12.5703125" style="2"/>
+    <x:col min="5" max="5" width="12.5703125" style="2"/>
+    <x:col min="6" max="7" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
     <x:col min="8" max="8" width="28.42578125" style="2" customWidth="1"/>
     <x:col min="9" max="16384" width="12.5703125" style="2"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F3" s="13" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H3" s="13" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E3" s="13" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G3" s="13" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H3" s="13" t="s">
-        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>20</x:v>
@@ -1515,7 +1519,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -1525,19 +1529,19 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>1000</x:v>
@@ -1546,7 +1550,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1556,19 +1560,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E6" s="4" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="E6" s="4" t="s">
-        <x:v>6</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>0</x:v>
@@ -1577,7 +1581,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -1586,19 +1590,19 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>100</x:v>
@@ -1607,7 +1611,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1617,19 +1621,19 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>28</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C8" s="3" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>20</x:v>
@@ -1638,7 +1642,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
@@ -1648,19 +1652,29 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>1</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D9" s="4"/>
-      <x:c r="E9" s="4"/>
-      <x:c r="F9" s="4"/>
-      <x:c r="G9" s="4"/>
-      <x:c r="H9" s="4"/>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E9" s="4" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F9" s="4">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G9" s="4">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H9" s="4" t="s">
+        <x:v>39</x:v>
+      </x:c>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
       <x:c r="K9" s="4"/>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -22,118 +22,118 @@
     <x:t>Icon/Icon_Item_Gold_1</x:t>
   </x:si>
   <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>의문의 모자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역에 나타나는 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화폐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>딸기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Strawberry_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>착용하면 공격력이 강해진다.</x:t>
   </x:si>
   <x:si>
+    <x:t>딸기, 겨울에 더 맛있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_DummyBox_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>MaxStackCount</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>딸기, 겨울에 더 맛있다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
   </x:si>
   <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_DummyBox_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>딸기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Starwberry_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>의문의 모자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지역에 나타나는 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
+    <x:t>Icon/Icon_Item_Strawberry_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Strawberry_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -377,7 +377,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -460,7 +459,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -495,7 +493,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -540,7 +537,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -584,7 +580,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -669,7 +664,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -690,7 +684,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -721,7 +714,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1437,80 +1429,80 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B3" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C3" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
+      <x:c r="F3" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E3" s="13" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G3" s="13" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>20</x:v>
@@ -1529,19 +1521,19 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>1000</x:v>
@@ -1560,19 +1552,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>0</x:v>
@@ -1581,7 +1573,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -1590,19 +1582,19 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>100</x:v>
@@ -1611,7 +1603,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1621,19 +1613,19 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>4</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>20</x:v>
@@ -1652,19 +1644,19 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F9" s="4">
         <x:v>20</x:v>
@@ -1673,7 +1665,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="19260" windowHeight="7368"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="19260" windowHeight="8664"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -16,124 +16,124 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
   <x:si>
-    <x:t>Icon/Icon_Item_Box_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Gold_1</x:t>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Cherry_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Orange_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>딸기, 겨울에 더 맛있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Melon_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체리, 선호하지 않는다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>멜론</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키위</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>딸기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오렌지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Pineapple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Strawberry_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키위, 키위새와 비슷하게 생겼다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Pineapple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파인애플, 통으로 보다는 잘라진 것을 사먹는 것이 좋다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오렌지, 껍질을 까는 것만 아니면 맛있게 먹을 것이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이상한 색의 멜론, 원래 색과는 거리가 먼 것 같다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파인애플</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
   </x:si>
   <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>의문의 모자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
   </x:si>
   <x:si>
     <x:t>Normal</x:t>
   </x:si>
   <x:si>
-    <x:t>옥수수다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지역에 나타나는 금화</x:t>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
     <x:t>IconPath</x:t>
   </x:si>
   <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
     <x:t>Description</x:t>
   </x:si>
   <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>딸기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Strawberry_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>착용하면 공격력이 강해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>딸기, 겨울에 더 맛있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_DummyBox_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+    <x:t>Item_Kiwi_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Kiwi_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Orange_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Melon_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Cherry_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Strawberry_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1429,89 +1429,89 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>6</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D3" s="14" t="s">
-        <x:v>16</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>36</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>31</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>15</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F4" s="4">
-        <x:v>20</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G4" s="4">
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -1521,28 +1521,28 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F5" s="4">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G5" s="4">
-        <x:v>1000</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1552,28 +1552,28 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D6" s="4" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="5" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D6" s="4" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F6" s="4">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G6" s="4">
-        <x:v>1</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -1582,28 +1582,28 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F7" s="4">
-        <x:v>100</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G7" s="4">
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1613,28 +1613,28 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F8" s="4">
-        <x:v>20</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G8" s="4">
-        <x:v>100</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
@@ -1644,28 +1644,28 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>34</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F9" s="4">
-        <x:v>20</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G9" s="4">
-        <x:v>100</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -14,126 +14,132 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Strawberry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Kiwi_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이상한 색의 멜론, 원래 색과는 거리가 먼 것 같다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오렌지, 껍질을 까는 것만 아니면 맛있게 먹을 것이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파인애플, 통으로 보다는 잘라진 것을 사먹는 것이 좋다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키위, 키위새와 비슷하게 생겼다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Strawberry_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Pineapple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파인애플</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>멜론</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>딸기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키위</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오렌지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>딸기, 겨울에 더 맛있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체리, 선호하지 않는다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Orange_1</x:t>
+  </x:si>
   <x:si>
     <x:t>MaxStackCount</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_Melon_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_Cherry_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Orange_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>딸기, 겨울에 더 맛있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Melon_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체리, 선호하지 않는다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>SellingPrice</x:t>
   </x:si>
   <x:si>
-    <x:t>멜론</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키위</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>딸기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오렌지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Pineapple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Strawberry_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키위, 키위새와 비슷하게 생겼다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Icon_Item_Pineapple_1</x:t>
   </x:si>
   <x:si>
-    <x:t>파인애플, 통으로 보다는 잘라진 것을 사먹는 것이 좋다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오렌지, 껍질을 까는 것만 아니면 맛있게 먹을 것이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이상한 색의 멜론, 원래 색과는 거리가 먼 것 같다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파인애플</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Kiwi_1</x:t>
+    <x:t>Icon/Icon_Item_Strawberry_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Orange_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Kiwi_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Icon_Item_Orange_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Icon_Item_Melon_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Cherry_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Strawberry_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1429,80 +1435,86 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:9" ht="12.300000000000001">
+      <x:c r="A2" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:9" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:8" ht="12.300000000000001">
-      <x:c r="A2" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="11" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B3" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C3" s="11" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="D3" s="14" t="s">
-        <x:v>30</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>0</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>7</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>32</x:v>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I3" s="12" t="s">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D4" s="4" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>100</x:v>
@@ -1511,7 +1523,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -1521,19 +1533,19 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>50</x:v>
@@ -1542,7 +1554,7 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1552,19 +1564,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>100</x:v>
@@ -1573,7 +1585,7 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -1582,19 +1594,19 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>200</x:v>
@@ -1603,7 +1615,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1613,19 +1625,19 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>50</x:v>
@@ -1634,7 +1646,7 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
@@ -1644,19 +1656,19 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="4">
         <x:v>200</x:v>
@@ -1665,9 +1677,11 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="I9" s="4"/>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I9" s="4" t="s">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J9" s="4"/>
       <x:c r="K9" s="4"/>
       <x:c r="L9" s="4"/>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -14,132 +14,147 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="47">
+  <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Melon_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체리, 선호하지 않는다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Cherry_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Orange_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>딸기, 겨울에 더 맛있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Kiwi_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키위</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>멜론</x:t>
+  </x:si>
+  <x:si>
+    <x:t>딸기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오렌지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이상한 색의 멜론, 원래 색과는 거리가 먼 것 같다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파인애플, 통으로 보다는 잘라진 것을 사먹는 것이 좋다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오렌지, 껍질을 까는 것만 아니면 맛있게 먹을 것이다.</x:t>
+  </x:si>
   <x:si>
     <x:t>2DPrefab/FieldItem_Strawberry</x:t>
   </x:si>
   <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Kiwi_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이상한 색의 멜론, 원래 색과는 거리가 먼 것 같다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오렌지, 껍질을 까는 것만 아니면 맛있게 먹을 것이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파인애플, 통으로 보다는 잘라진 것을 사먹는 것이 좋다.</x:t>
+    <x:t>2DPrefab/FieldItem_Pineapple</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파인애플</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Pineapple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Strawberry_1</x:t>
   </x:si>
   <x:si>
     <x:t>키위, 키위새와 비슷하게 생겼다.</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Strawberry_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Pineapple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파인애플</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>멜론</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>딸기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키위</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오렌지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>딸기, 겨울에 더 맛있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체리, 선호하지 않는다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Orange_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Melon_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Cherry_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Icon_Item_Pineapple_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Strawberry_1</x:t>
   </x:si>
   <x:si>
+    <x:t>2DPrefab/FieldItem_Orange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Melon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Cherry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Cherry_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Icon_Item_Orange_1</x:t>
   </x:si>
   <x:si>
+    <x:t>2DPrefab/FieldItem_Kiwi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Melon_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Icon_Item_Kiwi_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Melon_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Cherry_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -193,7 +208,7 @@
       <x:color rgb="ff008000"/>
     </x:font>
   </x:fonts>
-  <x:fills count="9">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -232,12 +247,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffd2f2db"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="ffffff00"/>
-        <x:bgColor rgb="ffd86dcd"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -370,7 +379,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
@@ -1430,91 +1439,92 @@
     <x:col min="5" max="5" width="12.5703125" style="2"/>
     <x:col min="6" max="7" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
     <x:col min="8" max="8" width="28.42578125" style="2" customWidth="1"/>
-    <x:col min="9" max="16384" width="12.5703125" style="2"/>
+    <x:col min="9" max="9" width="30.890625" style="2" customWidth="1"/>
+    <x:col min="10" max="16384" width="12.5703125" style="2"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:9" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C3" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
+      <x:c r="E3" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F3" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E3" s="13" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>6</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="I3" s="12" t="s">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>100</x:v>
@@ -1523,9 +1533,11 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="I4" s="4"/>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="I4" s="4" t="s">
+        <x:v>44</x:v>
+      </x:c>
       <x:c r="J4" s="4"/>
       <x:c r="K4" s="4"/>
       <x:c r="L4" s="4"/>
@@ -1533,19 +1545,19 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>50</x:v>
@@ -1554,9 +1566,11 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I5" s="4" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
       <x:c r="K5" s="4"/>
       <x:c r="L5" s="4"/>
@@ -1564,19 +1578,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D6" s="4" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C6" s="5" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D6" s="4" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>100</x:v>
@@ -1585,28 +1599,30 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="I6" s="4"/>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="I6" s="4" t="s">
+        <x:v>39</x:v>
+      </x:c>
       <x:c r="K6" s="4"/>
       <x:c r="L6" s="4"/>
       <x:c r="M6" s="4"/>
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>200</x:v>
@@ -1615,9 +1631,11 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I7" s="4" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
       <x:c r="K7" s="4"/>
       <x:c r="L7" s="4"/>
@@ -1625,19 +1643,19 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>12</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>50</x:v>
@@ -1646,9 +1664,11 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="I8" s="4"/>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I8" s="4" t="s">
+        <x:v>25</x:v>
+      </x:c>
       <x:c r="J8" s="4"/>
       <x:c r="K8" s="4"/>
       <x:c r="L8" s="4"/>
@@ -1656,19 +1676,19 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>11</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>28</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F9" s="4">
         <x:v>200</x:v>
@@ -1677,10 +1697,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I9" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="J9" s="4"/>
       <x:c r="K9" s="4"/>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="19260" windowHeight="8664"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="23580" windowHeight="8784"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -14,108 +14,153 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="47">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="56">
+  <x:si>
+    <x:t>Icon/Icon_Item_Kiwi_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Melon_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Orange_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Cherry_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Kiwi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemParameterList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>딸기, 겨울에 더 맛있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체리, 선호하지 않는다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeAtk</x:t>
+  </x:si>
   <x:si>
     <x:t>SellingPrice</x:t>
   </x:si>
   <x:si>
+    <x:t>SummonMonster</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Cherry_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_stand_1:2</x:t>
+  </x:si>
+  <x:si>
     <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
   </x:si>
   <x:si>
-    <x:t>MaxStackCount</x:t>
+    <x:t>Item_Orange_1</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Melon_1</x:t>
   </x:si>
   <x:si>
-    <x:t>체리, 선호하지 않는다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Cherry_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Orange_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>딸기, 겨울에 더 맛있다.</x:t>
+    <x:t>딸기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키위</x:t>
+  </x:si>
+  <x:si>
+    <x:t>멜론</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오렌지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파인애플, 통으로 보다는 잘라진 것을 사먹는 것이 좋다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오렌지, 껍질을 까는 것만 아니면 맛있게 먹을 것이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Pineapple</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이상한 색의 멜론, 원래 색과는 거리가 먼 것 같다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Strawberry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Kiwi_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
   </x:si>
   <x:si>
     <x:t>PrefabPath</x:t>
   </x:si>
   <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
     <x:t>Description</x:t>
   </x:si>
   <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RandomItem</x:t>
+  </x:si>
+  <x:si>
     <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Kiwi_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키위</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>멜론</x:t>
-  </x:si>
-  <x:si>
-    <x:t>딸기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오렌지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이상한 색의 멜론, 원래 색과는 거리가 먼 것 같다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파인애플, 통으로 보다는 잘라진 것을 사먹는 것이 좋다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오렌지, 껍질을 까는 것만 아니면 맛있게 먹을 것이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Strawberry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Pineapple</x:t>
+    <x:t>Item_Pineapple_1:2, Item_Strawberry_1:20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파인애플</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
   </x:si>
   <x:si>
     <x:t>Grade</x:t>
   </x:si>
   <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파인애플</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
+    <x:t>키위, 키위새와 비슷하게 생겼다.</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Pineapple_1</x:t>
@@ -124,37 +169,19 @@
     <x:t>Item_Strawberry_1</x:t>
   </x:si>
   <x:si>
-    <x:t>키위, 키위새와 비슷하게 생겼다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Icon_Item_Pineapple_1</x:t>
   </x:si>
   <x:si>
+    <x:t>2DPrefab/FieldItem_Cherry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Orange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Melon</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Icon_Item_Strawberry_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Orange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Melon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Cherry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Cherry_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Orange_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Kiwi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Melon_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Kiwi_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -392,6 +419,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -474,6 +502,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -508,6 +537,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -552,6 +582,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -595,6 +626,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -679,6 +711,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -699,6 +732,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -729,6 +763,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1440,91 +1475,105 @@
     <x:col min="6" max="7" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
     <x:col min="8" max="8" width="28.42578125" style="2" customWidth="1"/>
     <x:col min="9" max="9" width="30.890625" style="2" customWidth="1"/>
-    <x:col min="10" max="16384" width="12.5703125" style="2"/>
+    <x:col min="10" max="10" width="22.22265625" style="2" customWidth="1"/>
+    <x:col min="11" max="11" width="46.4453125" style="2" customWidth="1"/>
+    <x:col min="12" max="16384" width="12.5703125" style="2"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:9" ht="12.300000000000001">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:11" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J2" s="2" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="K2" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:11" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F3" s="13" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H3" s="13" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I3" s="12" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="I2" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:9" s="12" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B3" s="11" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C3" s="11" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E3" s="13" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G3" s="13" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H3" s="13" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="I3" s="12" t="s">
-        <x:v>8</x:v>
+      <x:c r="J3" s="12" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="K3" s="12" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>100</x:v>
@@ -1533,31 +1582,35 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="J4" s="4"/>
-      <x:c r="K4" s="4"/>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J4" s="4" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K4" s="4">
+        <x:v>50</x:v>
+      </x:c>
       <x:c r="L4" s="4"/>
       <x:c r="M4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>50</x:v>
@@ -1566,31 +1619,35 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I5" s="4" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="J5" s="4"/>
-      <x:c r="K5" s="4"/>
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="J5" s="4" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K5" s="4">
+        <x:v>700</x:v>
+      </x:c>
       <x:c r="L5" s="4"/>
       <x:c r="M5" s="4"/>
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>100</x:v>
@@ -1599,30 +1656,35 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>43</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I6" s="4" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J6" s="2" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K6" s="4" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="K6" s="4"/>
       <x:c r="L6" s="4"/>
       <x:c r="M6" s="4"/>
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>200</x:v>
@@ -1631,31 +1693,35 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I7" s="4" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="J7" s="4"/>
-      <x:c r="K7" s="4"/>
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="J7" s="4" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="K7" s="4" t="s">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="L7" s="4"/>
       <x:c r="M7" s="4"/>
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>34</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>50</x:v>
@@ -1664,10 +1730,10 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I8" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="J8" s="4"/>
       <x:c r="K8" s="4"/>
@@ -1676,19 +1742,19 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F9" s="4">
         <x:v>200</x:v>
@@ -1697,10 +1763,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I9" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J9" s="4"/>
       <x:c r="K9" s="4"/>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -14,174 +14,192 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="56">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="62">
+  <x:si>
+    <x:t>효과 없음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>랜덤 아이템</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 소환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체력을 50 회복한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력 700 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키위</x:t>
+  </x:si>
+  <x:si>
+    <x:t>딸기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>멜론</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오렌지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Kiwi_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RandomItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Pineapple</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Strawberry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이상한 색의 멜론, 원래 색과는 거리가 먼 것 같다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오렌지, 껍질을 까는 것만 아니면 맛있게 먹을 것이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파인애플, 통으로 보다는 잘라진 것을 사먹는 것이 좋다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Pineapple_1:2, Item_Strawberry_1:20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파인애플</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Pineapple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Strawberry_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키위, 키위새와 비슷하게 생겼다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_stand_1:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>딸기, 겨울에 더 맛있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체리, 선호하지 않는다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeAtk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Melon_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SummonMonster</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Cherry_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Orange_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Orange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Melon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Strawberry_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Pineapple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Cherry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemDescription</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Cherry_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Orange_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemParameterList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Melon_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Kiwi</x:t>
+  </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Kiwi_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Melon_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Orange_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Cherry_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Kiwi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemParameterList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>딸기, 겨울에 더 맛있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체리, 선호하지 않는다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StatChangeAtk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SummonMonster</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Cherry_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StatChangeHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_stand_1:2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Orange_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Melon_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>딸기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키위</x:t>
-  </x:si>
-  <x:si>
-    <x:t>멜론</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오렌지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파인애플, 통으로 보다는 잘라진 것을 사먹는 것이 좋다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오렌지, 껍질을 까는 것만 아니면 맛있게 먹을 것이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Pineapple</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이상한 색의 멜론, 원래 색과는 거리가 먼 것 같다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Strawberry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Kiwi_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RandomItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Pineapple_1:2, Item_Strawberry_1:20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파인애플</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키위, 키위새와 비슷하게 생겼다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Pineapple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Strawberry_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Pineapple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Cherry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Orange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Melon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Strawberry_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -419,7 +437,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -502,7 +519,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -537,7 +553,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -582,7 +597,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -626,7 +640,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -711,7 +724,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -732,7 +744,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -763,7 +774,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1477,103 +1487,110 @@
     <x:col min="9" max="9" width="30.890625" style="2" customWidth="1"/>
     <x:col min="10" max="10" width="22.22265625" style="2" customWidth="1"/>
     <x:col min="11" max="11" width="46.4453125" style="2" customWidth="1"/>
-    <x:col min="12" max="16384" width="12.5703125" style="2"/>
+    <x:col min="12" max="12" width="25.109375" style="2" customWidth="1"/>
+    <x:col min="13" max="16384" width="12.5703125" style="2"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:12" ht="12.300000000000001">
+      <x:c r="A2" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J2" s="2" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K2" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L2" s="2" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:12" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="11" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F3" s="13" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H3" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I3" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:11" ht="12.300000000000001">
-      <x:c r="A2" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="I2" s="2" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="J2" s="2" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="K2" s="2" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:11" s="12" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B3" s="11" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C3" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E3" s="13" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G3" s="13" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H3" s="13" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="I3" s="12" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="J3" s="12" t="s">
-        <x:v>36</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K3" s="12" t="s">
-        <x:v>5</x:v>
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="L3" s="12" t="s">
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>48</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>100</x:v>
@@ -1582,35 +1599,37 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I4" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J4" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K4" s="4">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L4" s="4"/>
+      <x:c r="L4" s="4" t="s">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="M4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>50</x:v>
@@ -1619,35 +1638,37 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I5" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J5" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="K5" s="4">
         <x:v>700</x:v>
       </x:c>
-      <x:c r="L5" s="4"/>
+      <x:c r="L5" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="M5" s="4"/>
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>100</x:v>
@@ -1656,35 +1677,37 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I6" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J6" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K6" s="4" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="L6" s="4"/>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L6" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="M6" s="4"/>
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>200</x:v>
@@ -1693,35 +1716,37 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I7" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J7" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K7" s="4" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="L7" s="4"/>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="L7" s="4" t="s">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="M7" s="4"/>
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>49</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>50</x:v>
@@ -1730,31 +1755,33 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I8" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J8" s="4"/>
       <x:c r="K8" s="4"/>
-      <x:c r="L8" s="4"/>
+      <x:c r="L8" s="4" t="s">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="M8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>50</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F9" s="4">
         <x:v>200</x:v>
@@ -1763,14 +1790,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I9" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J9" s="4"/>
       <x:c r="K9" s="4"/>
-      <x:c r="L9" s="4"/>
+      <x:c r="L9" s="4" t="s">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="M9" s="4"/>
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -16,154 +16,178 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="62">
   <x:si>
+    <x:t>UseItemParameterList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Kiwi_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Cherry_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Orange_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Kiwi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Melon_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파인애플, 잘라진 것을 먹는 게 편하다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Pineapple</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이상한 색의 멜론, 원래 색과는 거리가 먼 것 같다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Strawberry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Melon_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SummonMonster</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_stand_1:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Cherry_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체리, 선호하지 않는다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeAtk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>딸기, 겨울에 더 맛있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Orange_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Pineapple_1:2, Item_Strawberry_1:20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 소환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>랜덤 아이템</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파인애플</x:t>
+  </x:si>
+  <x:si>
     <x:t>효과 없음</x:t>
   </x:si>
   <x:si>
-    <x:t>랜덤 아이템</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 소환</x:t>
-  </x:si>
-  <x:si>
     <x:t>체력을 50 회복한다</x:t>
   </x:si>
   <x:si>
     <x:t>공격력 700 증가</x:t>
   </x:si>
   <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Kiwi_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RandomItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키위</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>딸기</x:t>
+  </x:si>
+  <x:si>
     <x:t>int</x:t>
   </x:si>
   <x:si>
-    <x:t>키위</x:t>
-  </x:si>
-  <x:si>
-    <x:t>딸기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체리</x:t>
+    <x:t>멜론</x:t>
   </x:si>
   <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
-    <x:t>멜론</x:t>
-  </x:si>
-  <x:si>
     <x:t>오렌지</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Kiwi_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RandomItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Pineapple</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Strawberry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이상한 색의 멜론, 원래 색과는 거리가 먼 것 같다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오렌지, 껍질을 까는 것만 아니면 맛있게 먹을 것이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파인애플, 통으로 보다는 잘라진 것을 사먹는 것이 좋다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Pineapple_1:2, Item_Strawberry_1:20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파인애플</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Pineapple_1</x:t>
   </x:si>
   <x:si>
+    <x:t>키위, 키위새와 비슷하게 생겼다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemDescription</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_Strawberry_1</x:t>
   </x:si>
   <x:si>
-    <x:t>키위, 키위새와 비슷하게 생겼다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_stand_1:2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>딸기, 겨울에 더 맛있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체리, 선호하지 않는다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StatChangeAtk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StatChangeHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Melon_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SummonMonster</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Cherry_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Orange_1</x:t>
+    <x:t>오렌지, 껍질을 까는 게 귀찮다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Cherry</x:t>
   </x:si>
   <x:si>
     <x:t>2DPrefab/FieldItem_Orange</x:t>
@@ -176,30 +200,6 @@
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Pineapple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Cherry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemDescription</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Cherry_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Orange_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemParameterList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Melon_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Kiwi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Kiwi_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -437,6 +437,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -519,6 +520,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -553,6 +555,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -597,6 +600,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -640,6 +644,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -724,6 +729,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -744,6 +750,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -774,6 +781,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1493,104 +1501,104 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K2" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="L2" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>9</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>18</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D3" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F3" s="13" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E3" s="13" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G3" s="13" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I3" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="J3" s="12" t="s">
-        <x:v>17</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K3" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L3" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>100</x:v>
@@ -1599,37 +1607,37 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I4" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J4" s="4" t="s">
-        <x:v>43</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K4" s="4">
         <x:v>50</x:v>
       </x:c>
       <x:c r="L4" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="M4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>46</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>50</x:v>
@@ -1638,37 +1646,37 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I5" s="4" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="I5" s="4" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="J5" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K5" s="4">
         <x:v>700</x:v>
       </x:c>
       <x:c r="L5" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="M5" s="4"/>
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>49</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>100</x:v>
@@ -1677,37 +1685,37 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I6" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J6" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K6" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="L6" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="M6" s="4"/>
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>48</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>200</x:v>
@@ -1716,37 +1724,37 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>56</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I7" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J7" s="4" t="s">
-        <x:v>47</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K7" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L7" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="M7" s="4"/>
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>35</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D8" s="4" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D8" s="4" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>50</x:v>
@@ -1755,33 +1763,33 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I8" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J8" s="4"/>
       <x:c r="K8" s="4"/>
       <x:c r="L8" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="M8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>40</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F9" s="4">
         <x:v>200</x:v>
@@ -1790,15 +1798,15 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I9" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J9" s="4"/>
       <x:c r="K9" s="4"/>
       <x:c r="L9" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="M9" s="4"/>
     </x:row>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -14,29 +14,188 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="62">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="63">
+  <x:si>
+    <x:t>키위, 키위새와 비슷하게 생겼다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Pineapple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Strawberry_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemDescription</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오렌지, 껍질을 까는 게 귀찮다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Kiwi_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력 700 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체력을 50 회복한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RandomItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Kiwi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Cherry_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Melon_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Orange_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Kiwi_1</x:t>
+  </x:si>
   <x:si>
     <x:t>UseItemParameterList</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Icon_Item_Kiwi_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Cherry_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Orange_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Kiwi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Melon_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>파인애플, 잘라진 것을 먹는 게 편하다.</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_Cherry_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Melon_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Orange_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체리, 선호하지 않는다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>딸기, 겨울에 더 맛있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeAtk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_stand_1:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SummonMonster</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>랜덤 아이템(미구현)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오렌지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>딸기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키위</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>멜론</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 소환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파인애플</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맛있다.(효과없음)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Pineapple_1:2, Item_Strawberry_1:20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안 좋아한다.(효과 없음)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Cherry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Orange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Melon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Pineapple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Strawberry_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>2DPrefab/FieldItem_Pineapple</x:t>
   </x:si>
   <x:si>
@@ -44,162 +203,6 @@
   </x:si>
   <x:si>
     <x:t>2DPrefab/FieldItem_Strawberry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StatChangeHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Melon_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SummonMonster</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_stand_1:2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Cherry_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체리, 선호하지 않는다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StatChangeAtk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>딸기, 겨울에 더 맛있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Orange_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Pineapple_1:2, Item_Strawberry_1:20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 소환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>랜덤 아이템</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파인애플</x:t>
-  </x:si>
-  <x:si>
-    <x:t>효과 없음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체력을 50 회복한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격력 700 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Kiwi_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RandomItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키위</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>딸기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>멜론</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오렌지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Pineapple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키위, 키위새와 비슷하게 생겼다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemDescription</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Strawberry_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오렌지, 껍질을 까는 게 귀찮다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Cherry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Orange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Melon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Strawberry_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Pineapple_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -437,7 +440,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -520,7 +522,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -555,7 +556,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -600,7 +600,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -644,7 +643,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -729,7 +727,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -750,7 +747,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -781,7 +777,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1501,104 +1496,104 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K2" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L2" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B3" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C3" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E3" s="13" t="s">
+      <x:c r="F3" s="13" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G3" s="13" t="s">
+      <x:c r="H3" s="13" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I3" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="H3" s="13" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I3" s="12" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="J3" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K3" s="12" t="s">
-        <x:v>0</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="L3" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>100</x:v>
@@ -1607,37 +1602,37 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I4" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J4" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="K4" s="4">
         <x:v>50</x:v>
       </x:c>
       <x:c r="L4" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="M4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>49</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>50</x:v>
@@ -1646,37 +1641,37 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I5" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J5" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K5" s="4">
         <x:v>700</x:v>
       </x:c>
       <x:c r="L5" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="M5" s="4"/>
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>51</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>100</x:v>
@@ -1685,37 +1680,37 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I6" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J6" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K6" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L6" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="M6" s="4"/>
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>200</x:v>
@@ -1724,37 +1719,37 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J7" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="K7" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="L7" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="M7" s="4"/>
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>52</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>50</x:v>
@@ -1763,33 +1758,33 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I8" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J8" s="4"/>
       <x:c r="K8" s="4"/>
       <x:c r="L8" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>55</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>47</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>20</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F9" s="4">
         <x:v>200</x:v>
@@ -1798,15 +1793,15 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I9" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J9" s="4"/>
       <x:c r="K9" s="4"/>
       <x:c r="L9" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M9" s="4"/>
     </x:row>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -16,193 +16,193 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="63">
   <x:si>
+    <x:t>UseItemParameterList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Melon_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파인애플, 잘라진 것을 먹는 게 편하다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Orange_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Cherry_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Kiwi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Kiwi_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Pineapple</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이상한 색의 멜론, 원래 색과는 거리가 먼 것 같다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/FieldItem_Strawberry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>딸기, 겨울에 더 맛있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_stand_1:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeAtk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Orange_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Cherry_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Melon_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체리, 선호하지 않는다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안 좋아한다.(효과 없음)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SummonMonster</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Kiwi_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RandomItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력 700 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체력을 50 회복한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>랜덤 아이템(미구현)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맛있다.(효과없음)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Pineapple_1:2,Item_Strawberry_1:20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Strawberry_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>키위, 키위새와 비슷하게 생겼다.</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Pineapple_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Strawberry_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>UseItemDescription</x:t>
   </x:si>
   <x:si>
     <x:t>오렌지, 껍질을 까는 게 귀찮다.</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Kiwi_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격력 700 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체력을 50 회복한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RandomItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Kiwi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Cherry_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Melon_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Orange_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Kiwi_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemParameterList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파인애플, 잘라진 것을 먹는 게 편하다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Cherry_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Melon_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Orange_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체리, 선호하지 않는다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>딸기, 겨울에 더 맛있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StatChangeAtk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_stand_1:2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SummonMonster</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StatChangeHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>랜덤 아이템(미구현)</x:t>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파인애플</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 소환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>딸기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>키위</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체리</x:t>
   </x:si>
   <x:si>
     <x:t>오렌지</x:t>
   </x:si>
   <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
     <x:t>int</x:t>
   </x:si>
   <x:si>
-    <x:t>딸기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>키위</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
     <x:t>멜론</x:t>
   </x:si>
   <x:si>
-    <x:t>체리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 소환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파인애플</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맛있다.(효과없음)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Pineapple_1:2, Item_Strawberry_1:20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안 좋아한다.(효과 없음)</x:t>
-  </x:si>
-  <x:si>
     <x:t>2DPrefab/FieldItem_Cherry</x:t>
   </x:si>
   <x:si>
     <x:t>2DPrefab/FieldItem_Orange</x:t>
   </x:si>
   <x:si>
+    <x:t>Icon/Icon_Item_Pineapple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Strawberry_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>2DPrefab/FieldItem_Melon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Pineapple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Strawberry_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Pineapple</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이상한 색의 멜론, 원래 색과는 거리가 먼 것 같다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/FieldItem_Strawberry</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -440,6 +440,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -522,6 +523,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -556,6 +558,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -600,6 +603,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -643,6 +647,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -727,6 +732,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -747,6 +753,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -777,6 +784,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1496,104 +1504,104 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K2" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L2" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F3" s="13" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H3" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="I3" s="12" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J3" s="12" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K3" s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L3" s="12" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="B3" s="11" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C3" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E3" s="13" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G3" s="13" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H3" s="13" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I3" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="J3" s="12" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="K3" s="12" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="L3" s="12" t="s">
-        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>100</x:v>
@@ -1602,37 +1610,37 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I4" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="J4" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="K4" s="4">
         <x:v>50</x:v>
       </x:c>
       <x:c r="L4" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="M4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>61</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>50</x:v>
@@ -1641,37 +1649,37 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I5" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J5" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K5" s="4">
         <x:v>700</x:v>
       </x:c>
       <x:c r="L5" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="M5" s="4"/>
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>100</x:v>
@@ -1680,37 +1688,37 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I6" s="4" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J6" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K6" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="L6" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="M6" s="4"/>
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>200</x:v>
@@ -1719,37 +1727,37 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I7" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J7" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K7" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L7" s="4" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M7" s="4"/>
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>1</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>50</x:v>
@@ -1758,33 +1766,33 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I8" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J8" s="4"/>
       <x:c r="K8" s="4"/>
       <x:c r="L8" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="M8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>38</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F9" s="4">
         <x:v>200</x:v>
@@ -1793,15 +1801,15 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I9" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J9" s="4"/>
       <x:c r="K9" s="4"/>
       <x:c r="L9" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M9" s="4"/>
     </x:row>
